--- a/output/pdf_financials_xlsx/CJ.xlsx
+++ b/output/pdf_financials_xlsx/CJ.xlsx
@@ -5953,28 +5953,28 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004686</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002653</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002239</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001459</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.003716</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.498</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="J118" s="1" t="inlineStr">
         <is>
@@ -5985,13 +5985,13 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-4.895</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08327900000000001</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.136513</v>
       </c>
     </row>
     <row r="119">
@@ -23724,7 +23724,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -29408,7 +29412,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E285" s="5" t="n">
         <v>-0.004686</v>
       </c>

--- a/output/pdf_financials_xlsx/CJ.xlsx
+++ b/output/pdf_financials_xlsx/CJ.xlsx
@@ -3737,16 +3737,16 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>1.487</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.001711</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.001751</v>
       </c>
     </row>
     <row r="71">
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>1.487</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>108.446</v>
+        <v>109.816</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>187.732</v>
+        <v>187.733711</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.001751</v>
       </c>
     </row>
     <row r="72">
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>20.069</v>
+        <v>18.582</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0</v>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.0194</v>
+        <v>0.017649</v>
       </c>
     </row>
     <row r="76">
@@ -4221,16 +4221,16 @@
         <v>0.001751868659903898</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.003245188411122038</v>
+        <v>0.004852113208770546</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.1219283839911023</v>
+        <v>0.1234164016474636</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>204.44666374084</v>
+        <v>204.4485270495579</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.003155125403068467</v>
+        <v>0.005250961738718272</v>
       </c>
     </row>
     <row r="81">
@@ -5569,45 +5569,43 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>6.4e-05</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.0006669999999999999</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.003702</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.006402</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.009145</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>9.874000000000001</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>10.017</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.458</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>7.69</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>8.058</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>7.937</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.009046999999999999</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.010415</v>
       </c>
     </row>
     <row r="111">
@@ -7737,7 +7735,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -23351,7 +23353,11 @@
           <t>Deferred tax expense 15</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -23428,7 +23434,11 @@
           <t>Accretion 9,10,11</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -25306,7 +25316,11 @@
           <t>Accretion 10,11</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -26094,7 +26108,11 @@
           <t>Deferred tax expense (recovery) 15</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27125,7 +27143,11 @@
           <t>Accretion 9,11</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -28934,7 +28956,11 @@
           <t>Deferred tax expense 15</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -29013,7 +29039,11 @@
           <t>Accretion 20</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -30340,7 +30370,11 @@
           <t>Accretion 19</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -31697,7 +31731,11 @@
           <t>Accretion 18</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -33852,7 +33890,11 @@
           <t>Accretion 18</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -35219,7 +35261,11 @@
           <t>Accretion 9</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E358" s="5" t="n">
         <v>6.4e-05</v>
       </c>
